--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I579"/>
+  <dimension ref="A1:I580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27657,6 +27657,53 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" s="3" t="inlineStr">
+        <is>
+          <t>236,459,490</t>
+        </is>
+      </c>
+      <c r="B580" s="3" t="inlineStr">
+        <is>
+          <t>2,072.01385</t>
+        </is>
+      </c>
+      <c r="C580" s="3" t="inlineStr">
+        <is>
+          <t>Sep 13, 2026</t>
+        </is>
+      </c>
+      <c r="D580" s="3" t="inlineStr">
+        <is>
+          <t>5,418.55361</t>
+        </is>
+      </c>
+      <c r="E580" s="3" t="inlineStr">
+        <is>
+          <t>-23.29665</t>
+        </is>
+      </c>
+      <c r="F580" s="3" t="inlineStr">
+        <is>
+          <t>-96.61455</t>
+        </is>
+      </c>
+      <c r="G580" s="3" t="inlineStr">
+        <is>
+          <t>5,713.183</t>
+        </is>
+      </c>
+      <c r="H580" s="3" t="inlineStr">
+        <is>
+          <t>6,862,972.350</t>
+        </is>
+      </c>
+      <c r="I580" s="3" t="inlineStr">
+        <is>
+          <t>182,186</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I580"/>
+  <dimension ref="A1:I581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27704,6 +27704,53 @@
         </is>
       </c>
     </row>
+    <row r="581">
+      <c r="A581" s="3" t="inlineStr">
+        <is>
+          <t>186,057,565</t>
+        </is>
+      </c>
+      <c r="B581" s="3" t="inlineStr">
+        <is>
+          <t>2,062.81418</t>
+        </is>
+      </c>
+      <c r="C581" s="3" t="inlineStr">
+        <is>
+          <t>Sep 14, 2026</t>
+        </is>
+      </c>
+      <c r="D581" s="3" t="inlineStr">
+        <is>
+          <t>5,379.00279</t>
+        </is>
+      </c>
+      <c r="E581" s="3" t="inlineStr">
+        <is>
+          <t>-9.19967</t>
+        </is>
+      </c>
+      <c r="F581" s="3" t="inlineStr">
+        <is>
+          <t>-39.55082</t>
+        </is>
+      </c>
+      <c r="G581" s="3" t="inlineStr">
+        <is>
+          <t>4,865.535</t>
+        </is>
+      </c>
+      <c r="H581" s="3" t="inlineStr">
+        <is>
+          <t>6,851,207.071</t>
+        </is>
+      </c>
+      <c r="I581" s="3" t="inlineStr">
+        <is>
+          <t>161,568</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I581"/>
+  <dimension ref="A1:I582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27751,6 +27751,53 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>171,639,239</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>2,087.70684</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>5,472.46437</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>24.89266</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>93.46158</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>5,048.692</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>6,864,198.582</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>152,421</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I582"/>
+  <dimension ref="A1:I583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27798,6 +27798,53 @@
         </is>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>195,264,330</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>2,092.97937</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>5,494.07408</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>5.27253</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>21.60971</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>5,562.092</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>6,891,161.492</t>
+        </is>
+      </c>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>168,020</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I583"/>
+  <dimension ref="A1:I584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27845,6 +27845,53 @@
         </is>
       </c>
     </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>230,305,192</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>2,101.15514</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>5,532.14854</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>8.17577</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>38.07446</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>6,554.26</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>6,923,732.620</t>
+        </is>
+      </c>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>183,531</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I584"/>
+  <dimension ref="A1:I585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27892,6 +27892,53 @@
         </is>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>277,695,612</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>2,121.18154</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>Sep 20, 2026</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>5,592.20688</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>20.0264</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>60.05834</t>
+        </is>
+      </c>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>7,473.825</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>6,945,547.913</t>
+        </is>
+      </c>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>201,639</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I585"/>
+  <dimension ref="A1:I586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27939,6 +27939,53 @@
         </is>
       </c>
     </row>
+    <row r="586">
+      <c r="A586" s="3" t="inlineStr">
+        <is>
+          <t>294,907,036</t>
+        </is>
+      </c>
+      <c r="B586" s="3" t="inlineStr">
+        <is>
+          <t>2,105.91687</t>
+        </is>
+      </c>
+      <c r="C586" s="3" t="inlineStr">
+        <is>
+          <t>Sep 21, 2026</t>
+        </is>
+      </c>
+      <c r="D586" s="3" t="inlineStr">
+        <is>
+          <t>5,550.49562</t>
+        </is>
+      </c>
+      <c r="E586" s="3" t="inlineStr">
+        <is>
+          <t>-15.26467</t>
+        </is>
+      </c>
+      <c r="F586" s="3" t="inlineStr">
+        <is>
+          <t>-41.71126</t>
+        </is>
+      </c>
+      <c r="G586" s="3" t="inlineStr">
+        <is>
+          <t>7,887.056</t>
+        </is>
+      </c>
+      <c r="H586" s="3" t="inlineStr">
+        <is>
+          <t>6,929,001.945</t>
+        </is>
+      </c>
+      <c r="I586" s="3" t="inlineStr">
+        <is>
+          <t>220,637</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dse_market_summary.xlsx
+++ b/dse_market_summary.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I586"/>
+  <dimension ref="A1:I587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27986,6 +27986,53 @@
         </is>
       </c>
     </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>267,998,402</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>2,122.7264</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>5,596.21859</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>16.55007</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>55.89822</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>8,446.967</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>6,944,297.002</t>
+        </is>
+      </c>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>217,984</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
